--- a/FIles_path.xlsx
+++ b/FIles_path.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyDocs\License management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D350523-2765-4DCD-9876-9DE0EDCF549B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CA26092-DF45-4887-872F-8B1705C6C088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{1237F1CC-5210-4BEB-9602-91362814278B}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="68">
   <si>
     <r>
       <t>app.py</t>
@@ -886,6 +887,12 @@
   </si>
   <si>
     <t>\templates\style_guide.html</t>
+  </si>
+  <si>
+    <t>\templates\excel_mapping.html</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Gafan87/license-analyzer/refs/heads/main/templates/excel_mapping.html</t>
   </si>
 </sst>
 </file>
@@ -940,7 +947,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -948,6 +955,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1262,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14AF7819-B5C4-45B3-8826-F0C8B37E4634}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.1328125" customWidth="1"/>
@@ -1519,7 +1530,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -1527,12 +1538,23 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
